--- a/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75E4D103-1AA8-4166-88EE-C8727C7F0282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{421D85EE-2979-4789-87A9-120FB1C14E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{421D85EE-2979-4789-87A9-120FB1C14E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A73E6647-BB3F-49FA-873C-AFEDAB536B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A73E6647-BB3F-49FA-873C-AFEDAB536B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85DCC7D2-74E4-44A6-83C0-6883E6219A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
